--- a/test_output_consolidated.xlsx
+++ b/test_output_consolidated.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="489" uniqueCount="98">
   <si>
     <t>#</t>
   </si>
@@ -103,91 +103,58 @@
     <t>Financial Audit</t>
   </si>
   <si>
-    <t>JUNE 1, 2026</t>
-  </si>
-  <si>
-    <t>JUNE 3, 2026</t>
-  </si>
-  <si>
-    <t>JUNE 9, 2026</t>
-  </si>
-  <si>
-    <t>2026IAD209</t>
-  </si>
-  <si>
-    <t>2026IAD211</t>
-  </si>
-  <si>
-    <t>2026IAD212</t>
-  </si>
-  <si>
-    <t>2026IAD214</t>
-  </si>
-  <si>
-    <t>2026IAD215</t>
-  </si>
-  <si>
-    <t>2026IAD220</t>
-  </si>
-  <si>
-    <t>2026IAD221</t>
-  </si>
-  <si>
-    <t>20090013</t>
-  </si>
-  <si>
-    <t>20230197</t>
-  </si>
-  <si>
-    <t>20240060</t>
-  </si>
-  <si>
-    <t>20230087</t>
-  </si>
-  <si>
-    <t>20240154</t>
-  </si>
-  <si>
-    <t>20170046</t>
-  </si>
-  <si>
-    <t>20170015</t>
-  </si>
-  <si>
-    <t>Michelle Mae Lazaro Mesa</t>
-  </si>
-  <si>
-    <t>Gerrie Mia Tabotabo Montejo</t>
-  </si>
-  <si>
-    <t>Mirz Celene Lucero Dula ugon</t>
-  </si>
-  <si>
-    <t>Jennifer Bulalaque Cabintoy</t>
-  </si>
-  <si>
-    <t>Jennel Kate Lagman Fortin</t>
-  </si>
-  <si>
-    <t>Jugine Jean Viloria Corpuz</t>
-  </si>
-  <si>
-    <t>Timothy Paculan So</t>
+    <t>NOVEMBER 20, 2025</t>
+  </si>
+  <si>
+    <t>JANUARY 16, 2026</t>
   </si>
   <si>
     <t>None</t>
   </si>
   <si>
-    <t>May 29,</t>
-  </si>
-  <si>
-    <t>June 2,</t>
-  </si>
-  <si>
-    <t>June 5,</t>
-  </si>
-  <si>
-    <t>June 8,</t>
+    <t>20251AD418</t>
+  </si>
+  <si>
+    <t>2026IAD013</t>
+  </si>
+  <si>
+    <t>20230142</t>
+  </si>
+  <si>
+    <t>20160023</t>
+  </si>
+  <si>
+    <t>20240227</t>
+  </si>
+  <si>
+    <t>Emerito Bondoc and Antoinette Joy Sambrano</t>
+  </si>
+  <si>
+    <t>Antoinette Joy Balolong Sambrano</t>
+  </si>
+  <si>
+    <t>Emerito Maninang Bondoc</t>
+  </si>
+  <si>
+    <t>Ma. Angelica Cadorna Cuevas</t>
+  </si>
+  <si>
+    <t>001</t>
+  </si>
+  <si>
+    <t>002</t>
+  </si>
+  <si>
+    <t>003</t>
+  </si>
+  <si>
+    <t>066</t>
+  </si>
+  <si>
+    <t>January 14,</t>
+  </si>
+  <si>
+    <t>2025</t>
   </si>
   <si>
     <t>2026</t>
@@ -196,187 +163,148 @@
     <t>Ignore or Disregard Office/Operation Best Practices -3</t>
   </si>
   <si>
+    <t>Cash/Fund/Collection Overage (₱1,000.00 and above) -4</t>
+  </si>
+  <si>
     <t>Nonconformity With The Written Policies, Guidelines, Process And Procedures -4</t>
   </si>
   <si>
-    <t>Cash/Fund/Collection Shortage (below ₱3,000.00) -4</t>
-  </si>
-  <si>
-    <t>Cash/Fund/Collection Overage (₱1,000.00 and above) -4</t>
-  </si>
-  <si>
-    <t>No Findings 10</t>
+    <t>Cash/Fund/Collection Shortage (₱3,000.00 and above) -8</t>
+  </si>
+  <si>
+    <t>Missing, Misused or Lost Of Documents/Asset(s) -3</t>
+  </si>
+  <si>
+    <t>INCOMPLETE CV INFORMATION - DATE</t>
+  </si>
+  <si>
+    <t>CASH OVERAGE: P19,510.04</t>
+  </si>
+  <si>
+    <t>INCONSISTENT USING OF PCV</t>
   </si>
   <si>
     <t>LATE PREPARATION OF PCV</t>
   </si>
   <si>
-    <t>WITHOUT STAMPED “PAID” IN SUPPORTING DOCUMENTS</t>
-  </si>
-  <si>
-    <t>BUDGET RELEASE WITHOUT PRIOR PCR</t>
-  </si>
-  <si>
-    <t>INCOMPLETE DETAILS IN PCV - PAYEE</t>
-  </si>
-  <si>
-    <t>INCOMPLETE RECEIPT INFORMATION</t>
-  </si>
-  <si>
-    <t>INCOMPLETE DETAILS IN PCV - APPROVED BY</t>
-  </si>
-  <si>
-    <t>CASH SHORTAGE: (P2,713.99)</t>
-  </si>
-  <si>
-    <t>NO PREPARATION OF PCV</t>
-  </si>
-  <si>
-    <t>UNCANCELLED PCV</t>
-  </si>
-  <si>
     <t>NO DOCUMENT USED FOR CASH TAKEN FROM THE FUND</t>
   </si>
   <si>
-    <t>INACCURATE MONITORING OF FUND</t>
-  </si>
-  <si>
-    <t>DEPLETED FUND – 24.92%</t>
-  </si>
-  <si>
-    <t>CASH OVERAGE: P3,530.95</t>
-  </si>
-  <si>
-    <t>OUTDATED MONITORING</t>
-  </si>
-  <si>
-    <t>MIXING OF PETTY CASH AND REVOLVING FUND</t>
-  </si>
-  <si>
-    <t>NO CASH SHORTAGE/OVERAGE</t>
-  </si>
-  <si>
-    <t>She was not able to prepare its PCV since the petty cash request form was submitted late by the requestor. She further explained that she does not prepare a PCV without the corresponding PCR.</t>
-  </si>
-  <si>
-    <t>She was supposed to stamp it before our arrival.</t>
-  </si>
-  <si>
-    <t>This practice is followed to avoid revisions to the amount indicated in the PCR, as the actual expense is incurred before the form is prepared.</t>
-  </si>
-  <si>
-    <t>She was uncertain whether the payee should be indicated as the Lalamove rider or herself.</t>
-  </si>
-  <si>
-    <t>She did not notice that these details were omitted.</t>
-  </si>
-  <si>
-    <t>She was busy at the time and forgot to obtain the signature of her Immediate Head, Mr. Lito Carpio. During confirmation, she stated that Mr. Carpio had been in the office the previous day; however, she forgot to have the document signed.</t>
-  </si>
-  <si>
-    <t>The P1,024.00 shortage was due to unreturned fund used for CA#2600905.</t>
-  </si>
-  <si>
-    <t>She had overlooked the printing of the receipt and the preparation of the PCV.</t>
-  </si>
-  <si>
-    <t>She had mistakenly prepared the PCV in advance but was unable to cancel it afterward.</t>
-  </si>
-  <si>
-    <t>She was not able to process her latest replenishment earlier due to busy schedule.</t>
-  </si>
-  <si>
-    <t>This was her personal cash and that she overlooked the receipt, which she only discovered during the audit while organizing and submitting the supporting documents.</t>
-  </si>
-  <si>
-    <t>She forgot to prepare the PCV after receiving the receipt, resulting in a delay in recording the transaction.</t>
-  </si>
-  <si>
-    <t>Prepare the PCV at the same time the receipt was received.</t>
-  </si>
-  <si>
-    <t>Stamp the supporting documents once the PCF transaction has been completed.</t>
-  </si>
-  <si>
-    <t>The PCR form should be submitted prior to the release of the budget.</t>
-  </si>
-  <si>
-    <t>In case of doubt, the requestor’s name should also be indicated as the payee to avoid confusion and ensure completeness of PCV information.</t>
-  </si>
-  <si>
-    <t>Review the issued memo dated March 3, 2026 – “Indication of Complete Company Name and TIN on Sales Invoices/Official Receipts”.</t>
-  </si>
-  <si>
-    <t>Ensure that all required signatures are secured before filing or processing PCVs to maintain proper authorization and compliance with established procedures.</t>
-  </si>
-  <si>
-    <t>Ms. Jennel Kate Fortin should explain further regarding this shortage.</t>
-  </si>
-  <si>
-    <t>Promptly prepare the PCV after completing the fund transaction.</t>
-  </si>
-  <si>
-    <t>Prepare PCVs only when needed and to promptly cancel any PCVs that will no longer be used.</t>
-  </si>
-  <si>
-    <t>Properly document the transfer of cash to ensure clear accountability and proper tracking of funds.</t>
-  </si>
-  <si>
-    <t>Ensure that all replenishments and related transactions are accurately and timely recorded in the monitoring records and regularly reconciled to prevent discrepancies.</t>
-  </si>
-  <si>
-    <t>Submit the replenishment form once the fund reaches 25% utilization to avoid fund depletion and ensure timely processing amid multiple transactions.</t>
-  </si>
-  <si>
-    <t>Return the personal cash and thoroughly review all receipts to ensure that all are properly accounted for.</t>
-  </si>
-  <si>
-    <t>Use the revolving fund and cash on hand as the mode of payment to avoid the use of personal cash.</t>
-  </si>
-  <si>
-    <t>Update records after each transaction or at least every other day, considering workload.</t>
+    <t>INCOMPLETE RECEIPT INFORMATION - SUPPLIER NAME, CONTACT NUMBER, SIGNATURE AND ADDRESS</t>
+  </si>
+  <si>
+    <t>INCORRECT RECEIPT INFORMATION</t>
+  </si>
+  <si>
+    <t>USE OF CASH ADVANCE OUTSIDE ITS PURPOSE</t>
+  </si>
+  <si>
+    <t>UNACCOUNTED CASH: (P6,829.00)</t>
+  </si>
+  <si>
+    <t>NO DAILY BALANCING / MONITORING OF FUND</t>
+  </si>
+  <si>
+    <t>INCOMPLETE DETAILS IN PCV - RECIPIENT'S SIGNATURE, PCV DATE, APPROVAL</t>
+  </si>
+  <si>
+    <t>SKIPPED AND MISSING PCV</t>
+  </si>
+  <si>
+    <t>NO PRE-PRINTED SERIES AND USING GENERIC TRANSMITTAL FORM</t>
+  </si>
+  <si>
+    <t>He really forgot to write the date and only noticed it during the audit.</t>
+  </si>
+  <si>
+    <t>She only prepares PCV for expenses without official receipts.</t>
+  </si>
+  <si>
+    <t>She only prepares the PCV when she is ready to replenish.</t>
+  </si>
+  <si>
+    <t>She forgot to document the disbursed amount to Ms. Pama and assumed that the cash would be returned immediately by Ms. Salvador.</t>
+  </si>
+  <si>
+    <t>She sometimes forgets to include all the necessary information.</t>
+  </si>
+  <si>
+    <t>The receipt was from Ms. Cruz and she did not notice the date because she focused only on the amount.</t>
+  </si>
+  <si>
+    <t>The P17,170.00 was temporarily used to support her revolving fund.</t>
+  </si>
+  <si>
+    <t>She frequently switches bags, which is why the fund cash is stored at home.</t>
+  </si>
+  <si>
+    <t>She had another replenishment amounting of P2,724.00 that had not been deposited into her Metrobank online account.</t>
+  </si>
+  <si>
+    <t>She was unaware that these acknowledgments were required, as no one informed her when the fund was handed over.</t>
+  </si>
+  <si>
+    <t>Always indicate the date of transaction for monitoring purposes.</t>
+  </si>
+  <si>
+    <t>The custodian disbursed fund to Ms.</t>
+  </si>
+  <si>
+    <t>Review Policy No. 3 of Policies and Procedures on Revolving Fund - Version 1.0 requiring all disbursements to be supported by cash vouchers with official receipts or invoices attached.</t>
+  </si>
+  <si>
+    <t>Ensure unofficial receipts include the store name, address, date, contact number, items bought, price, and owner’s signature.</t>
+  </si>
+  <si>
+    <t>Double-check documents before accepting them to avoid confusion regarding the transaction.</t>
+  </si>
+  <si>
+    <t>Use cash advances only for their intended purpose to avoid mixing funds and to maintain clear and accurate records.</t>
+  </si>
+  <si>
+    <t>Review the Art. III: Section 11, Failure or Refusal to Follow Proper Procedures in Carrying Out Assigned Tasks.</t>
+  </si>
+  <si>
+    <t>Monitor her revolving fund regularly to track its usage and ensure all expenses and documents are properly accounted for.</t>
+  </si>
+  <si>
+    <t>Ensure petty cash vouchers are signed and date to confirm that transactions are properly recorded.</t>
+  </si>
+  <si>
+    <t>If a mistake is made on a PCV, mark it as “Cancelled” instead of tearing it, so the PCV numbers remain consecutive.</t>
+  </si>
+  <si>
+    <t>Maintain good coordination to avoid misunderstandings and ensure clear and efficient work.</t>
+  </si>
+  <si>
+    <t>Should explain further regarding the undocumented transaction with Ms. Salvador.</t>
+  </si>
+  <si>
+    <t>Should provide an explanation regarding this matter.</t>
+  </si>
+  <si>
+    <t>Use the transmittal form with carbon copies and complete all required details according to its purpose.</t>
   </si>
   <si>
     <t>Patricia Anne S. Del Rosario</t>
   </si>
   <si>
-    <t>Cris Canonoy</t>
-  </si>
-  <si>
     <t>Sarina Amuraw</t>
   </si>
   <si>
     <t>Do Some Adjustment</t>
   </si>
   <si>
-    <t>Maintaining Status Quo</t>
-  </si>
-  <si>
     <t>First Time</t>
   </si>
   <si>
-    <t>Not Applicable</t>
-  </si>
-  <si>
-    <t>Ms.</t>
-  </si>
-  <si>
-    <t>During the audit, Ms.</t>
-  </si>
-  <si>
     <t>Follow-up with HR</t>
   </si>
   <si>
-    <t>No Case/Issue</t>
-  </si>
-  <si>
     <t>Individual</t>
   </si>
   <si>
     <t>Anne</t>
-  </si>
-  <si>
-    <t>Cris</t>
   </si>
   <si>
     <t>Sab</t>
@@ -737,7 +665,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AA18"/>
+  <dimension ref="A1:AA22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:27">
@@ -837,55 +765,55 @@
         <v>29</v>
       </c>
       <c r="E2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F2" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="G2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H2" t="s">
+        <v>41</v>
+      </c>
+      <c r="I2" t="s">
+        <v>31</v>
+      </c>
+      <c r="J2" t="s">
         <v>46</v>
       </c>
-      <c r="H2" t="s">
+      <c r="K2" t="s">
+        <v>48</v>
+      </c>
+      <c r="L2" t="s">
         <v>53</v>
       </c>
-      <c r="I2" t="s">
-        <v>54</v>
-      </c>
-      <c r="J2" t="s">
-        <v>58</v>
-      </c>
-      <c r="K2" t="s">
-        <v>59</v>
-      </c>
-      <c r="L2" t="s">
-        <v>64</v>
-      </c>
       <c r="M2" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="N2" t="s">
+        <v>76</v>
+      </c>
+      <c r="O2" t="s">
+        <v>31</v>
+      </c>
+      <c r="P2" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>31</v>
+      </c>
+      <c r="R2" t="s">
         <v>92</v>
       </c>
-      <c r="O2" t="s">
-        <v>53</v>
-      </c>
-      <c r="P2" t="s">
-        <v>107</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>53</v>
-      </c>
-      <c r="R2" t="s">
-        <v>110</v>
-      </c>
       <c r="S2" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="T2" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="V2" t="s">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="W2">
         <v>-3</v>
@@ -897,10 +825,10 @@
         <v>-3</v>
       </c>
       <c r="Z2" t="s">
-        <v>118</v>
+        <v>95</v>
       </c>
       <c r="AA2" t="s">
-        <v>119</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3" spans="1:27">
@@ -917,55 +845,55 @@
         <v>29</v>
       </c>
       <c r="E3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F3" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="G3" t="s">
+        <v>38</v>
+      </c>
+      <c r="H3" t="s">
+        <v>42</v>
+      </c>
+      <c r="I3" t="s">
+        <v>31</v>
+      </c>
+      <c r="J3" t="s">
         <v>46</v>
       </c>
-      <c r="H3" t="s">
-        <v>53</v>
-      </c>
-      <c r="I3" t="s">
+      <c r="K3" t="s">
+        <v>49</v>
+      </c>
+      <c r="L3" t="s">
         <v>54</v>
       </c>
-      <c r="J3" t="s">
-        <v>58</v>
-      </c>
-      <c r="K3" t="s">
-        <v>60</v>
-      </c>
-      <c r="L3" t="s">
-        <v>65</v>
-      </c>
       <c r="M3" t="s">
-        <v>81</v>
+        <v>31</v>
       </c>
       <c r="N3" t="s">
+        <v>77</v>
+      </c>
+      <c r="O3" t="s">
+        <v>31</v>
+      </c>
+      <c r="P3" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>31</v>
+      </c>
+      <c r="R3" t="s">
+        <v>92</v>
+      </c>
+      <c r="S3" t="s">
         <v>93</v>
       </c>
-      <c r="O3" t="s">
-        <v>53</v>
-      </c>
-      <c r="P3" t="s">
-        <v>107</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>53</v>
-      </c>
-      <c r="R3" t="s">
-        <v>110</v>
-      </c>
-      <c r="S3" t="s">
-        <v>112</v>
-      </c>
       <c r="T3" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="V3" t="s">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="W3">
         <v>-4</v>
@@ -977,10 +905,10 @@
         <v>-4</v>
       </c>
       <c r="Z3" t="s">
-        <v>118</v>
+        <v>95</v>
       </c>
       <c r="AA3" t="s">
-        <v>119</v>
+        <v>96</v>
       </c>
     </row>
     <row r="4" spans="1:27">
@@ -997,75 +925,75 @@
         <v>29</v>
       </c>
       <c r="E4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F4" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="G4" t="s">
+        <v>38</v>
+      </c>
+      <c r="H4" t="s">
+        <v>42</v>
+      </c>
+      <c r="I4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J4" t="s">
         <v>46</v>
       </c>
-      <c r="H4" t="s">
-        <v>53</v>
-      </c>
-      <c r="I4" t="s">
-        <v>54</v>
-      </c>
-      <c r="J4" t="s">
-        <v>58</v>
-      </c>
       <c r="K4" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="L4" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="M4" t="s">
-        <v>82</v>
+        <v>67</v>
       </c>
       <c r="N4" t="s">
+        <v>78</v>
+      </c>
+      <c r="O4" t="s">
+        <v>31</v>
+      </c>
+      <c r="P4" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>31</v>
+      </c>
+      <c r="R4" t="s">
+        <v>92</v>
+      </c>
+      <c r="S4" t="s">
+        <v>93</v>
+      </c>
+      <c r="T4" t="s">
+        <v>31</v>
+      </c>
+      <c r="V4" t="s">
         <v>94</v>
       </c>
-      <c r="O4" t="s">
-        <v>53</v>
-      </c>
-      <c r="P4" t="s">
-        <v>107</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>53</v>
-      </c>
-      <c r="R4" t="s">
-        <v>110</v>
-      </c>
-      <c r="S4" t="s">
-        <v>112</v>
-      </c>
-      <c r="T4" t="s">
-        <v>53</v>
-      </c>
-      <c r="V4" t="s">
-        <v>116</v>
-      </c>
       <c r="W4">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="X4">
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="Z4" t="s">
-        <v>118</v>
+        <v>95</v>
       </c>
       <c r="AA4" t="s">
-        <v>119</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5" spans="1:27">
       <c r="A5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B5" t="s">
         <v>27</v>
@@ -1077,75 +1005,75 @@
         <v>29</v>
       </c>
       <c r="E5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F5" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="G5" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="H5" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="I5" t="s">
-        <v>54</v>
+        <v>31</v>
       </c>
       <c r="J5" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="K5" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="L5" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="M5" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="N5" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="O5" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="P5" t="s">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="Q5" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="R5" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="S5" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="T5" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="V5" t="s">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="W5">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="X5">
         <v>0</v>
       </c>
       <c r="Y5">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="Z5" t="s">
-        <v>118</v>
+        <v>95</v>
       </c>
       <c r="AA5" t="s">
-        <v>119</v>
+        <v>96</v>
       </c>
     </row>
     <row r="6" spans="1:27">
       <c r="A6">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>27</v>
@@ -1154,78 +1082,78 @@
         <v>28</v>
       </c>
       <c r="D6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" t="s">
         <v>34</v>
       </c>
-      <c r="F6" t="s">
-        <v>41</v>
-      </c>
       <c r="G6" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="H6" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="I6" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="J6" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="K6" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="L6" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="M6" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="N6" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="O6" t="s">
-        <v>53</v>
+        <v>87</v>
       </c>
       <c r="P6" t="s">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="Q6" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="R6" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="S6" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="T6" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="V6" t="s">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="W6">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="X6">
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="Z6" t="s">
-        <v>118</v>
+        <v>95</v>
       </c>
       <c r="AA6" t="s">
-        <v>119</v>
+        <v>96</v>
       </c>
     </row>
     <row r="7" spans="1:27">
       <c r="A7">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>27</v>
@@ -1234,78 +1162,78 @@
         <v>28</v>
       </c>
       <c r="D7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E7" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="F7" t="s">
+        <v>34</v>
+      </c>
+      <c r="G7" t="s">
+        <v>38</v>
+      </c>
+      <c r="H7" t="s">
         <v>42</v>
       </c>
-      <c r="G7" t="s">
-        <v>49</v>
-      </c>
-      <c r="H7" t="s">
-        <v>53</v>
-      </c>
       <c r="I7" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="J7" t="s">
+        <v>46</v>
+      </c>
+      <c r="K7" t="s">
+        <v>48</v>
+      </c>
+      <c r="L7" t="s">
         <v>58</v>
       </c>
-      <c r="K7" t="s">
-        <v>60</v>
-      </c>
-      <c r="L7" t="s">
-        <v>69</v>
-      </c>
       <c r="M7" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="N7" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="O7" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="P7" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="Q7" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="R7" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="S7" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="T7" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="V7" t="s">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="W7">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="X7">
         <v>0</v>
       </c>
       <c r="Y7">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="Z7" t="s">
-        <v>118</v>
+        <v>95</v>
       </c>
       <c r="AA7" t="s">
-        <v>120</v>
+        <v>96</v>
       </c>
     </row>
     <row r="8" spans="1:27">
       <c r="A8">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
@@ -1314,78 +1242,78 @@
         <v>28</v>
       </c>
       <c r="D8" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E8" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F8" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="G8" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="H8" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="I8" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="J8" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="K8" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="L8" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="M8" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
       <c r="N8" t="s">
-        <v>98</v>
+        <v>80</v>
       </c>
       <c r="O8" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="P8" t="s">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="Q8" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="R8" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="S8" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="T8" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="V8" t="s">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="W8">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="X8">
         <v>0</v>
       </c>
       <c r="Y8">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="Z8" t="s">
-        <v>118</v>
+        <v>95</v>
       </c>
       <c r="AA8" t="s">
-        <v>119</v>
+        <v>96</v>
       </c>
     </row>
     <row r="9" spans="1:27">
       <c r="A9">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B9" t="s">
         <v>27</v>
@@ -1394,58 +1322,58 @@
         <v>28</v>
       </c>
       <c r="D9" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E9" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F9" t="s">
+        <v>34</v>
+      </c>
+      <c r="G9" t="s">
+        <v>38</v>
+      </c>
+      <c r="H9" t="s">
         <v>43</v>
       </c>
-      <c r="G9" t="s">
-        <v>50</v>
-      </c>
-      <c r="H9" t="s">
-        <v>53</v>
-      </c>
       <c r="I9" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="J9" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="K9" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="L9" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="M9" t="s">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="N9" t="s">
-        <v>99</v>
+        <v>81</v>
       </c>
       <c r="O9" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="P9" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="Q9" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="R9" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="S9" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="T9" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="V9" t="s">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="W9">
         <v>-3</v>
@@ -1457,15 +1385,15 @@
         <v>-3</v>
       </c>
       <c r="Z9" t="s">
-        <v>118</v>
+        <v>95</v>
       </c>
       <c r="AA9" t="s">
-        <v>119</v>
+        <v>97</v>
       </c>
     </row>
     <row r="10" spans="1:27">
       <c r="A10">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B10" t="s">
         <v>27</v>
@@ -1474,58 +1402,58 @@
         <v>28</v>
       </c>
       <c r="D10" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E10" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F10" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="G10" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="H10" t="s">
+        <v>44</v>
+      </c>
+      <c r="I10" t="s">
+        <v>31</v>
+      </c>
+      <c r="J10" t="s">
+        <v>46</v>
+      </c>
+      <c r="K10" t="s">
+        <v>48</v>
+      </c>
+      <c r="L10" t="s">
         <v>53</v>
       </c>
-      <c r="I10" t="s">
-        <v>55</v>
-      </c>
-      <c r="J10" t="s">
-        <v>58</v>
-      </c>
-      <c r="K10" t="s">
-        <v>59</v>
-      </c>
-      <c r="L10" t="s">
-        <v>72</v>
-      </c>
       <c r="M10" t="s">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="N10" t="s">
-        <v>100</v>
+        <v>76</v>
       </c>
       <c r="O10" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="P10" t="s">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="Q10" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="R10" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="S10" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="T10" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="V10" t="s">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="W10">
         <v>-3</v>
@@ -1537,15 +1465,15 @@
         <v>-3</v>
       </c>
       <c r="Z10" t="s">
-        <v>118</v>
+        <v>95</v>
       </c>
       <c r="AA10" t="s">
-        <v>119</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11" spans="1:27">
       <c r="A11">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B11" t="s">
         <v>27</v>
@@ -1554,78 +1482,78 @@
         <v>28</v>
       </c>
       <c r="D11" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E11" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F11" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="G11" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="H11" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="I11" t="s">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="J11" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="K11" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="L11" t="s">
-        <v>73</v>
+        <v>54</v>
       </c>
       <c r="M11" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="N11" t="s">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="O11" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="P11" t="s">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="Q11" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="R11" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="S11" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="T11" t="s">
-        <v>114</v>
+        <v>31</v>
       </c>
       <c r="V11" t="s">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="W11">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="X11">
         <v>0</v>
       </c>
       <c r="Y11">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="Z11" t="s">
-        <v>118</v>
+        <v>95</v>
       </c>
       <c r="AA11" t="s">
-        <v>119</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12" spans="1:27">
       <c r="A12">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B12" t="s">
         <v>27</v>
@@ -1634,78 +1562,78 @@
         <v>28</v>
       </c>
       <c r="D12" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E12" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F12" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="G12" t="s">
+        <v>38</v>
+      </c>
+      <c r="H12" t="s">
+        <v>42</v>
+      </c>
+      <c r="I12" t="s">
+        <v>31</v>
+      </c>
+      <c r="J12" t="s">
+        <v>46</v>
+      </c>
+      <c r="K12" t="s">
         <v>50</v>
       </c>
-      <c r="H12" t="s">
-        <v>53</v>
-      </c>
-      <c r="I12" t="s">
+      <c r="L12" t="s">
         <v>55</v>
       </c>
-      <c r="J12" t="s">
-        <v>58</v>
-      </c>
-      <c r="K12" t="s">
-        <v>59</v>
-      </c>
-      <c r="L12" t="s">
-        <v>74</v>
-      </c>
       <c r="M12" t="s">
-        <v>53</v>
+        <v>67</v>
       </c>
       <c r="N12" t="s">
-        <v>102</v>
+        <v>78</v>
       </c>
       <c r="O12" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="P12" t="s">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="Q12" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="R12" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="S12" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="T12" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="V12" t="s">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="W12">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="X12">
         <v>0</v>
       </c>
       <c r="Y12">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="Z12" t="s">
-        <v>118</v>
+        <v>95</v>
       </c>
       <c r="AA12" t="s">
-        <v>119</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13" spans="1:27">
       <c r="A13">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B13" t="s">
         <v>27</v>
@@ -1714,78 +1642,78 @@
         <v>28</v>
       </c>
       <c r="D13" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E13" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F13" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="G13" t="s">
+        <v>38</v>
+      </c>
+      <c r="H13" t="s">
+        <v>42</v>
+      </c>
+      <c r="I13" t="s">
+        <v>31</v>
+      </c>
+      <c r="J13" t="s">
+        <v>46</v>
+      </c>
+      <c r="K13" t="s">
         <v>50</v>
       </c>
-      <c r="H13" t="s">
-        <v>53</v>
-      </c>
-      <c r="I13" t="s">
-        <v>55</v>
-      </c>
-      <c r="J13" t="s">
-        <v>58</v>
-      </c>
-      <c r="K13" t="s">
-        <v>59</v>
-      </c>
       <c r="L13" t="s">
-        <v>75</v>
+        <v>56</v>
       </c>
       <c r="M13" t="s">
-        <v>89</v>
+        <v>68</v>
       </c>
       <c r="N13" t="s">
-        <v>103</v>
+        <v>78</v>
       </c>
       <c r="O13" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="P13" t="s">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="Q13" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="R13" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="S13" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="T13" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="V13" t="s">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="W13">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="X13">
         <v>0</v>
       </c>
       <c r="Y13">
-        <v>-3</v>
+        <v>-4</v>
       </c>
       <c r="Z13" t="s">
-        <v>118</v>
+        <v>95</v>
       </c>
       <c r="AA13" t="s">
-        <v>119</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14" spans="1:27">
       <c r="A14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B14" t="s">
         <v>27</v>
@@ -1794,58 +1722,58 @@
         <v>28</v>
       </c>
       <c r="D14" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E14" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="F14" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="G14" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="H14" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="I14" t="s">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="J14" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="K14" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="L14" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="M14" t="s">
+        <v>69</v>
+      </c>
+      <c r="N14" t="s">
+        <v>78</v>
+      </c>
+      <c r="O14" t="s">
+        <v>87</v>
+      </c>
+      <c r="P14" t="s">
         <v>90</v>
       </c>
-      <c r="N14" t="s">
-        <v>104</v>
-      </c>
-      <c r="O14" t="s">
-        <v>53</v>
-      </c>
-      <c r="P14" t="s">
-        <v>109</v>
-      </c>
       <c r="Q14" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="R14" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="S14" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="T14" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="V14" t="s">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="W14">
         <v>-4</v>
@@ -1857,15 +1785,15 @@
         <v>-4</v>
       </c>
       <c r="Z14" t="s">
-        <v>118</v>
+        <v>95</v>
       </c>
       <c r="AA14" t="s">
-        <v>121</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15" spans="1:27">
       <c r="A15">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B15" t="s">
         <v>27</v>
@@ -1874,58 +1802,58 @@
         <v>28</v>
       </c>
       <c r="D15" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E15" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="F15" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="G15" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="H15" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="I15" t="s">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="J15" t="s">
+        <v>46</v>
+      </c>
+      <c r="K15" t="s">
+        <v>48</v>
+      </c>
+      <c r="L15" t="s">
         <v>58</v>
       </c>
-      <c r="K15" t="s">
-        <v>59</v>
-      </c>
-      <c r="L15" t="s">
-        <v>64</v>
-      </c>
       <c r="M15" t="s">
-        <v>91</v>
+        <v>70</v>
       </c>
       <c r="N15" t="s">
-        <v>105</v>
+        <v>79</v>
       </c>
       <c r="O15" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="P15" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
       <c r="Q15" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="R15" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="S15" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="T15" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="V15" t="s">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="W15">
         <v>-3</v>
@@ -1937,15 +1865,15 @@
         <v>-3</v>
       </c>
       <c r="Z15" t="s">
-        <v>118</v>
+        <v>95</v>
       </c>
       <c r="AA15" t="s">
-        <v>121</v>
+        <v>96</v>
       </c>
     </row>
     <row r="16" spans="1:27">
       <c r="A16">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B16" t="s">
         <v>27</v>
@@ -1954,58 +1882,58 @@
         <v>28</v>
       </c>
       <c r="D16" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E16" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="F16" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="G16" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="H16" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="I16" t="s">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="J16" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="K16" t="s">
+        <v>48</v>
+      </c>
+      <c r="L16" t="s">
         <v>59</v>
       </c>
-      <c r="L16" t="s">
-        <v>77</v>
-      </c>
       <c r="M16" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="N16" t="s">
-        <v>106</v>
+        <v>80</v>
       </c>
       <c r="O16" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="P16" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
       <c r="Q16" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="R16" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="S16" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="T16" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="V16" t="s">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="W16">
         <v>-3</v>
@@ -2017,15 +1945,15 @@
         <v>-3</v>
       </c>
       <c r="Z16" t="s">
-        <v>118</v>
+        <v>95</v>
       </c>
       <c r="AA16" t="s">
-        <v>121</v>
+        <v>96</v>
       </c>
     </row>
     <row r="17" spans="1:27">
       <c r="A17">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B17" t="s">
         <v>27</v>
@@ -2034,58 +1962,58 @@
         <v>28</v>
       </c>
       <c r="D17" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E17" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="F17" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="G17" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="H17" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="I17" t="s">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="J17" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="K17" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="L17" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="M17" t="s">
-        <v>53</v>
+        <v>72</v>
       </c>
       <c r="N17" t="s">
-        <v>53</v>
+        <v>81</v>
       </c>
       <c r="O17" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="P17" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
       <c r="Q17" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="R17" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="S17" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="T17" t="s">
-        <v>115</v>
+        <v>31</v>
       </c>
       <c r="V17" t="s">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="W17">
         <v>-3</v>
@@ -2097,10 +2025,10 @@
         <v>-3</v>
       </c>
       <c r="Z17" t="s">
-        <v>118</v>
+        <v>95</v>
       </c>
       <c r="AA17" t="s">
-        <v>121</v>
+        <v>96</v>
       </c>
     </row>
     <row r="18" spans="1:27">
@@ -2114,73 +2042,393 @@
         <v>28</v>
       </c>
       <c r="D18" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E18" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="F18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G18" t="s">
+        <v>40</v>
+      </c>
+      <c r="H18" t="s">
+        <v>31</v>
+      </c>
+      <c r="I18" t="s">
         <v>45</v>
       </c>
-      <c r="G18" t="s">
+      <c r="J18" t="s">
+        <v>47</v>
+      </c>
+      <c r="K18" t="s">
+        <v>51</v>
+      </c>
+      <c r="L18" t="s">
+        <v>61</v>
+      </c>
+      <c r="M18" t="s">
+        <v>73</v>
+      </c>
+      <c r="N18" t="s">
+        <v>82</v>
+      </c>
+      <c r="O18" t="s">
+        <v>88</v>
+      </c>
+      <c r="P18" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>31</v>
+      </c>
+      <c r="R18" t="s">
+        <v>92</v>
+      </c>
+      <c r="S18" t="s">
+        <v>93</v>
+      </c>
+      <c r="T18" t="s">
+        <v>31</v>
+      </c>
+      <c r="V18" t="s">
+        <v>94</v>
+      </c>
+      <c r="W18">
+        <v>-8</v>
+      </c>
+      <c r="X18">
+        <v>0</v>
+      </c>
+      <c r="Y18">
+        <v>-8</v>
+      </c>
+      <c r="Z18" t="s">
+        <v>95</v>
+      </c>
+      <c r="AA18" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="19" spans="1:27">
+      <c r="A19">
+        <v>2</v>
+      </c>
+      <c r="B19" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" t="s">
+        <v>28</v>
+      </c>
+      <c r="D19" t="s">
+        <v>30</v>
+      </c>
+      <c r="E19" t="s">
+        <v>33</v>
+      </c>
+      <c r="F19" t="s">
+        <v>36</v>
+      </c>
+      <c r="G19" t="s">
+        <v>40</v>
+      </c>
+      <c r="H19" t="s">
+        <v>31</v>
+      </c>
+      <c r="I19" t="s">
+        <v>45</v>
+      </c>
+      <c r="J19" t="s">
+        <v>47</v>
+      </c>
+      <c r="K19" t="s">
+        <v>48</v>
+      </c>
+      <c r="L19" t="s">
+        <v>62</v>
+      </c>
+      <c r="M19" t="s">
+        <v>74</v>
+      </c>
+      <c r="N19" t="s">
+        <v>83</v>
+      </c>
+      <c r="O19" t="s">
+        <v>31</v>
+      </c>
+      <c r="P19" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>31</v>
+      </c>
+      <c r="R19" t="s">
+        <v>92</v>
+      </c>
+      <c r="S19" t="s">
+        <v>93</v>
+      </c>
+      <c r="T19" t="s">
+        <v>31</v>
+      </c>
+      <c r="V19" t="s">
+        <v>94</v>
+      </c>
+      <c r="W19">
+        <v>-3</v>
+      </c>
+      <c r="X19">
+        <v>0</v>
+      </c>
+      <c r="Y19">
+        <v>-3</v>
+      </c>
+      <c r="Z19" t="s">
+        <v>95</v>
+      </c>
+      <c r="AA19" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="20" spans="1:27">
+      <c r="A20">
+        <v>3</v>
+      </c>
+      <c r="B20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20" t="s">
+        <v>28</v>
+      </c>
+      <c r="D20" t="s">
+        <v>30</v>
+      </c>
+      <c r="E20" t="s">
+        <v>33</v>
+      </c>
+      <c r="F20" t="s">
+        <v>36</v>
+      </c>
+      <c r="G20" t="s">
+        <v>40</v>
+      </c>
+      <c r="H20" t="s">
+        <v>31</v>
+      </c>
+      <c r="I20" t="s">
+        <v>45</v>
+      </c>
+      <c r="J20" t="s">
+        <v>47</v>
+      </c>
+      <c r="K20" t="s">
+        <v>48</v>
+      </c>
+      <c r="L20" t="s">
+        <v>63</v>
+      </c>
+      <c r="M20" t="s">
+        <v>75</v>
+      </c>
+      <c r="N20" t="s">
+        <v>84</v>
+      </c>
+      <c r="O20" t="s">
+        <v>31</v>
+      </c>
+      <c r="P20" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>31</v>
+      </c>
+      <c r="R20" t="s">
+        <v>92</v>
+      </c>
+      <c r="S20" t="s">
+        <v>93</v>
+      </c>
+      <c r="T20" t="s">
+        <v>31</v>
+      </c>
+      <c r="V20" t="s">
+        <v>94</v>
+      </c>
+      <c r="W20">
+        <v>-3</v>
+      </c>
+      <c r="X20">
+        <v>0</v>
+      </c>
+      <c r="Y20">
+        <v>-3</v>
+      </c>
+      <c r="Z20" t="s">
+        <v>95</v>
+      </c>
+      <c r="AA20" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="21" spans="1:27">
+      <c r="A21">
+        <v>4</v>
+      </c>
+      <c r="B21" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21" t="s">
+        <v>28</v>
+      </c>
+      <c r="D21" t="s">
+        <v>30</v>
+      </c>
+      <c r="E21" t="s">
+        <v>33</v>
+      </c>
+      <c r="F21" t="s">
+        <v>36</v>
+      </c>
+      <c r="G21" t="s">
+        <v>40</v>
+      </c>
+      <c r="H21" t="s">
+        <v>31</v>
+      </c>
+      <c r="I21" t="s">
+        <v>45</v>
+      </c>
+      <c r="J21" t="s">
+        <v>47</v>
+      </c>
+      <c r="K21" t="s">
         <v>52</v>
       </c>
-      <c r="H18" t="s">
-        <v>53</v>
-      </c>
-      <c r="I18" t="s">
-        <v>57</v>
-      </c>
-      <c r="J18" t="s">
-        <v>58</v>
-      </c>
-      <c r="K18" t="s">
-        <v>63</v>
-      </c>
-      <c r="L18" t="s">
-        <v>79</v>
-      </c>
-      <c r="M18" t="s">
-        <v>53</v>
-      </c>
-      <c r="N18" t="s">
-        <v>53</v>
-      </c>
-      <c r="O18" t="s">
-        <v>53</v>
-      </c>
-      <c r="P18" t="s">
-        <v>108</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>53</v>
-      </c>
-      <c r="R18" t="s">
-        <v>111</v>
-      </c>
-      <c r="S18" t="s">
-        <v>113</v>
-      </c>
-      <c r="T18" t="s">
-        <v>53</v>
-      </c>
-      <c r="V18" t="s">
-        <v>117</v>
-      </c>
-      <c r="W18">
-        <v>10</v>
-      </c>
-      <c r="X18">
-        <v>1</v>
-      </c>
-      <c r="Y18">
-        <v>11</v>
-      </c>
-      <c r="Z18" t="s">
-        <v>118</v>
-      </c>
-      <c r="AA18" t="s">
-        <v>120</v>
+      <c r="L21" t="s">
+        <v>64</v>
+      </c>
+      <c r="M21" t="s">
+        <v>31</v>
+      </c>
+      <c r="N21" t="s">
+        <v>85</v>
+      </c>
+      <c r="O21" t="s">
+        <v>31</v>
+      </c>
+      <c r="P21" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>31</v>
+      </c>
+      <c r="R21" t="s">
+        <v>92</v>
+      </c>
+      <c r="S21" t="s">
+        <v>93</v>
+      </c>
+      <c r="T21" t="s">
+        <v>31</v>
+      </c>
+      <c r="V21" t="s">
+        <v>94</v>
+      </c>
+      <c r="W21">
+        <v>-3</v>
+      </c>
+      <c r="X21">
+        <v>0</v>
+      </c>
+      <c r="Y21">
+        <v>-3</v>
+      </c>
+      <c r="Z21" t="s">
+        <v>95</v>
+      </c>
+      <c r="AA21" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="22" spans="1:27">
+      <c r="A22">
+        <v>5</v>
+      </c>
+      <c r="B22" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22" t="s">
+        <v>28</v>
+      </c>
+      <c r="D22" t="s">
+        <v>30</v>
+      </c>
+      <c r="E22" t="s">
+        <v>33</v>
+      </c>
+      <c r="F22" t="s">
+        <v>36</v>
+      </c>
+      <c r="G22" t="s">
+        <v>40</v>
+      </c>
+      <c r="H22" t="s">
+        <v>31</v>
+      </c>
+      <c r="I22" t="s">
+        <v>45</v>
+      </c>
+      <c r="J22" t="s">
+        <v>47</v>
+      </c>
+      <c r="K22" t="s">
+        <v>48</v>
+      </c>
+      <c r="L22" t="s">
+        <v>65</v>
+      </c>
+      <c r="M22" t="s">
+        <v>31</v>
+      </c>
+      <c r="N22" t="s">
+        <v>86</v>
+      </c>
+      <c r="O22" t="s">
+        <v>89</v>
+      </c>
+      <c r="P22" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>31</v>
+      </c>
+      <c r="R22" t="s">
+        <v>92</v>
+      </c>
+      <c r="S22" t="s">
+        <v>93</v>
+      </c>
+      <c r="T22" t="s">
+        <v>31</v>
+      </c>
+      <c r="V22" t="s">
+        <v>94</v>
+      </c>
+      <c r="W22">
+        <v>-3</v>
+      </c>
+      <c r="X22">
+        <v>0</v>
+      </c>
+      <c r="Y22">
+        <v>-3</v>
+      </c>
+      <c r="Z22" t="s">
+        <v>95</v>
+      </c>
+      <c r="AA22" t="s">
+        <v>97</v>
       </c>
     </row>
   </sheetData>
